--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.30201894124045</v>
+        <v>10.61157807795157</v>
       </c>
       <c r="D2" t="n">
-        <v>65.18570344409763</v>
+        <v>10.59267680966586</v>
       </c>
       <c r="E2" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F2" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.0353938388886</v>
+        <v>5.855751498819398</v>
       </c>
       <c r="D3" t="n">
-        <v>35.93625868319027</v>
+        <v>5.839642036018419</v>
       </c>
       <c r="E3" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F3" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.23215853692851</v>
+        <v>2.150225762250883</v>
       </c>
       <c r="D4" t="n">
-        <v>13.02059879292806</v>
+        <v>2.11584730385081</v>
       </c>
       <c r="E4" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F4" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.21343215660158</v>
+        <v>5.397182725447758</v>
       </c>
       <c r="D5" t="n">
-        <v>33.00610850235338</v>
+        <v>5.363492631632425</v>
       </c>
       <c r="E5" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F5" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.43832447533028</v>
+        <v>9.821227727241171</v>
       </c>
       <c r="D6" t="n">
-        <v>33.5562637894354</v>
+        <v>5.452892865783252</v>
       </c>
       <c r="E6" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F6" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>81.76717250530888</v>
+        <v>13.28716553211269</v>
       </c>
       <c r="D7" t="n">
-        <v>25.29592755004814</v>
+        <v>4.110588226882823</v>
       </c>
       <c r="E7" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F7" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.4110970392722</v>
+        <v>7.379303268881733</v>
       </c>
       <c r="D8" t="n">
-        <v>43.52834169686317</v>
+        <v>7.073355525740266</v>
       </c>
       <c r="E8" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F8" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.45770796167552</v>
+        <v>6.249377543772272</v>
       </c>
       <c r="D9" t="n">
-        <v>38.54213301608647</v>
+        <v>6.263096615114051</v>
       </c>
       <c r="E9" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F9" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>69.19318170010163</v>
+        <v>11.24389202626651</v>
       </c>
       <c r="D10" t="n">
-        <v>14.39041175982412</v>
+        <v>2.338441910971419</v>
       </c>
       <c r="E10" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F10" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.12492378083835</v>
+        <v>5.382800114386233</v>
       </c>
       <c r="D11" t="n">
-        <v>33.37899273872733</v>
+        <v>5.424086320043192</v>
       </c>
       <c r="E11" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F11" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.53252663425941</v>
+        <v>4.636535578067154</v>
       </c>
       <c r="D12" t="n">
-        <v>28.37271196755077</v>
+        <v>4.610565694727001</v>
       </c>
       <c r="E12" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F12" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69772588794556</v>
+        <v>4.988380456791154</v>
       </c>
       <c r="D13" t="n">
-        <v>30.98442192448141</v>
+        <v>5.034968562728229</v>
       </c>
       <c r="E13" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F13" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.87549565341681</v>
+        <v>6.479768043680233</v>
       </c>
       <c r="D14" t="n">
-        <v>40.15392309373137</v>
+        <v>6.525012502731348</v>
       </c>
       <c r="E14" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F14" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.808987539037902</v>
+        <v>1.431460475093659</v>
       </c>
       <c r="D15" t="n">
-        <v>9.094314485581853</v>
+        <v>1.477826103907051</v>
       </c>
       <c r="E15" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F15" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.81931655421453</v>
+        <v>5.495638940059862</v>
       </c>
       <c r="D16" t="n">
-        <v>30.10685701806437</v>
+        <v>4.892364265435461</v>
       </c>
       <c r="E16" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F16" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.98577428965728</v>
+        <v>5.685188322069308</v>
       </c>
       <c r="D17" t="n">
-        <v>34.87322945790156</v>
+        <v>5.666899786909004</v>
       </c>
       <c r="E17" t="n">
-        <v>18.96667216217315</v>
+        <v>3.082084226353137</v>
       </c>
       <c r="F17" t="n">
-        <v>12.82052509000349</v>
+        <v>2.083335327125567</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
